--- a/RoomImport/Восстановленный Пример импорта все типы помещений.xlsx
+++ b/RoomImport/Восстановленный Пример импорта все типы помещений.xlsx
@@ -80,7 +80,7 @@
     <t>Квартира</t>
   </si>
   <si>
-    <t>лит. 1</t>
+    <t>лит. 1.1</t>
   </si>
   <si>
     <t>№ првк 1 --1</t>
@@ -128,15 +128,18 @@
     <t>Машиноместо</t>
   </si>
   <si>
+    <t>литер 1-1</t>
+  </si>
+  <si>
     <t>№ маш 2 -1-1</t>
   </si>
   <si>
+    <t>лит. 1/1</t>
+  </si>
+  <si>
     <t>№ маш 2 -1-2</t>
   </si>
   <si>
-    <t>лит. 1.2</t>
-  </si>
-  <si>
     <t>№ маш 2 -1-3</t>
   </si>
   <si>
@@ -179,7 +182,20 @@
     <t>ап3</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Tahoma"/>
+        <color theme="1" tint="0"/>
+        <sz val="10"/>
+      </rPr>
+      <t>офисноепомещение№1(№8,9,10)</t>
+    </r>
+  </si>
+  <si>
     <t>Нежилое помещение</t>
+  </si>
+  <si>
+    <t>литер 1.4</t>
   </si>
 </sst>
 </file>
@@ -190,7 +206,7 @@
     <numFmt co:extendedFormatCode="General" formatCode="General" numFmtId="1000"/>
     <numFmt co:extendedFormatCode="0" formatCode="0" numFmtId="1001"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <color theme="1" tint="0"/>
@@ -204,6 +220,11 @@
     <font>
       <name val="Times New Roman"/>
       <b val="true"/>
+      <color theme="1" tint="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
       <color theme="1" tint="0"/>
       <sz val="10"/>
     </font>
@@ -301,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf applyFont="true" applyNumberFormat="true" borderId="0" fillId="0" fontId="1" numFmtId="1000" quotePrefix="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf applyFont="true" applyNumberFormat="true" borderId="0" fillId="0" fontId="1" numFmtId="1000" quotePrefix="false"/>
     <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="1" fillId="2" fontId="2" numFmtId="1001" quotePrefix="false">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -329,6 +350,9 @@
     </xf>
     <xf applyAlignment="true" applyBorder="true" applyFont="true" borderId="5" fillId="0" fontId="0" quotePrefix="false">
       <alignment wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFont="true" borderId="4" fillId="0" fontId="3" quotePrefix="false">
+      <alignment horizontal="center" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -642,7 +666,7 @@
         <v>6</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="O3" s="7" t="n">
         <v>10</v>
@@ -1327,8 +1351,8 @@
       <c r="G3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>20</v>
+      <c r="H3" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="I3" s="9" t="n">
         <v>-1</v>
@@ -1349,7 +1373,7 @@
         <v>800006</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row outlineLevel="0" r="4">
@@ -1371,8 +1395,8 @@
       <c r="G4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>20</v>
+      <c r="H4" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="I4" s="9" t="n">
         <v>-1</v>
@@ -1393,7 +1417,7 @@
         <v>800007</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
@@ -1437,7 +1461,7 @@
         <v>800008</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1523,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>3</v>
@@ -1547,7 +1571,7 @@
         <v>800006</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row outlineLevel="0" r="4">
@@ -1567,7 +1591,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>3</v>
@@ -1609,7 +1633,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>3</v>
@@ -1717,10 +1741,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>4</v>
+        <v>43</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="I3" s="9" t="n">
         <v>1</v>
@@ -1759,10 +1783,10 @@
         <v>2</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>4</v>
+        <v>43</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="I4" s="9" t="n">
         <v>1</v>
@@ -1783,7 +1807,7 @@
         <v>800007</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
@@ -1803,10 +1827,10 @@
         <v>3</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>4</v>
+        <v>43</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>1</v>
@@ -1911,7 +1935,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>4</v>
@@ -1953,7 +1977,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>4</v>
@@ -1995,7 +2019,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>4</v>
@@ -2019,7 +2043,7 @@
         <v>800008</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2105,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>4</v>
@@ -2147,7 +2171,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>4</v>
@@ -2171,7 +2195,7 @@
         <v>800007</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
@@ -2191,7 +2215,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>4</v>
@@ -2215,7 +2239,7 @@
         <v>800008</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2301,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>4</v>
@@ -2325,7 +2349,7 @@
         <v>800006</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row outlineLevel="0" r="4">
@@ -2345,7 +2369,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>4</v>
@@ -2369,7 +2393,7 @@
         <v>800007</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
@@ -2389,7 +2413,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>4</v>
@@ -2413,7 +2437,7 @@
         <v>800008</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2495,14 +2519,14 @@
       <c r="E3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="7" t="n">
-        <v>1</v>
+      <c r="F3" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>4</v>
+        <v>55</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="I3" s="9" t="n">
         <v>100</v>
@@ -2541,10 +2565,10 @@
         <v>2</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>4</v>
+        <v>55</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="I4" s="9" t="n">
         <v>100</v>
@@ -2583,10 +2607,10 @@
         <v>3</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>4</v>
+        <v>55</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>100</v>
